--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3054-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3054-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5070B40-D22E-4319-A643-DF51E5EC9F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE87A07-03DA-4D8B-8AF3-50D889DF95A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B6764A0A-3042-4933-A3DE-FCCCA7582FBB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{CE75B208-062A-479A-A837-4CAD8D88E23A}"/>
   </bookViews>
   <sheets>
     <sheet name="3054-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1463,30 +1463,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F57F4F-BAC8-444F-BC68-CC51D84BA05B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF3E8E8-2BFE-4431-BDEA-017D23FE74D1}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="8" width="7.125" customWidth="1"/>
-    <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="8" width="6.109375" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1676,7 +1676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2020</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2019</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2018</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2017</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2016</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2015</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2014</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2013</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2012</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2011</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2010</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2009</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2008</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2007</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2006</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2005</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2004</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2003</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2002</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2001</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2000</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>42</v>
       </c>
